--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0034.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0034.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Im… Im lặng nào. Ta phải đếm đã…</t>
+          <t>Im… Im lặng nào. Tao phải đếm đã…</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Ta biết cậu đang tức giận, nhưng bình tĩnh lại đi...</t>
+          <t>Tao biết cậu đang tức giận, nhưng bình tĩnh lại đi...</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Chỉ là thứ ta viết lúc rảnh rỗi thôi. Ta chỉ muốn chia sẻ nó với cậu…</t>
+          <t>Chỉ là thứ tao viết lúc rảnh rỗi thôi. Tao chỉ muốn chia sẻ nó với cậu…</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Làm sao ta biết được cậu lại coi trọng chuyện đó đến vậy? Chính vì thế nên ta mới...</t>
+          <t>Làm sao tao biết được cậu lại coi trọng chuyện đó đến vậy? Chính vì thế nên tao mới...</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chính vì thế mà cậu mới lợi dụng cơ hội này để bán nó cho ta, lại còn bắt ta phải thực hiện đủ thứ nghi lễ vớ vẩn này nữa!</t>
+          <t>Chính vì thế mà cậu mới lợi dụng cơ hội này để bán nó cho tao, lại còn bắt tao phải thực hiện đủ thứ nghi lễ vớ vẩn này nữa!</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Chỉ là vài con Cua Chuông thôi mà. Ta trả lại cho ngươi đấy...</t>
+          <t>Chỉ là vài con Cua Chuông thôi mà. Tao trả lại cho mày đấy...</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ta mua nguyên bộ đồ câu chỉ để bắt mấy con Cua đó, cộng thêm cả tôm để nuôi chúng nữa!</t>
+          <t>Tao mua nguyên bộ đồ câu chỉ để bắt mấy con Cua đó, cộng thêm cả tôm để nuôi chúng nữa!</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Ta muốn lấy lại tiền của ta. Cần câu. Con tôm. &lt;i&gt;Vua Áo Giáp&lt;/i&gt;. Tất cả mấy Shell Credit ngươi đã cuỗm của ta!</t>
+          <t>Tao muốn lấy lại tiền của tao. Cần câu. Con tôm. &lt;i&gt;Vua Áo Giáp&lt;/i&gt;. Tất cả mấy Shell Credit mày đã cuỗm của tao!</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Nhấn nút Công cụ để sử dụng Freeze Frame Camera.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} nút Công cụ để sử dụng Freeze Frame Camera.</t>
         </is>
       </c>
     </row>
